--- a/artfynd/A 2093-2026 artfynd.xlsx
+++ b/artfynd/A 2093-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1090,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16591428</v>
+        <v>134806595</v>
       </c>
       <c r="B6" t="n">
-        <v>88980</v>
+        <v>97810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,39 +1101,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3295</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Corner</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandhult, Vg</t>
+          <t>Sandhult, Sandhult, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>347984</v>
+        <v>348161</v>
       </c>
       <c r="R6" t="n">
-        <v>6433120</v>
+        <v>6433128</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1155,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,29 +1179,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67560295</v>
+        <v>134806661</v>
       </c>
       <c r="B7" t="n">
-        <v>88980</v>
+        <v>97810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,39 +1208,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3295</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Corner</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandhult, Vg</t>
+          <t>Sandhult, Sandhult, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>347998</v>
+        <v>348137</v>
       </c>
       <c r="R7" t="n">
-        <v>6433110</v>
+        <v>6433123</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,12 +1262,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1271,29 +1286,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bobby Sulistyo, Patrik Lauthers, Ellen Larsson</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16591432</v>
+        <v>134806772</v>
       </c>
       <c r="B8" t="n">
-        <v>88982</v>
+        <v>97810</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1315,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3297</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aprikosfingersvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Clavulinopsis luteoalba</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Rea) Corner</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandhult, Vg</t>
+          <t>Sandhult, Sandhult, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>347984</v>
+        <v>348140</v>
       </c>
       <c r="R8" t="n">
-        <v>6433120</v>
+        <v>6433118</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1369,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1371,29 +1393,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6948089</v>
+        <v>134806430</v>
       </c>
       <c r="B9" t="n">
-        <v>89080</v>
+        <v>96423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,43 +1422,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4373</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sprödvaxing</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrocybe ceracea</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wulfen) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandhult, Vg</t>
+          <t>Sandhult, Sandhult, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>347997</v>
+        <v>348161</v>
       </c>
       <c r="R9" t="n">
-        <v>6433103</v>
+        <v>6433157</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1461,12 +1476,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-09-17</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-09-17</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,29 +1500,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16591416</v>
+        <v>16591428</v>
       </c>
       <c r="B10" t="n">
-        <v>89080</v>
+        <v>88980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4373</v>
+        <v>3295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprödvaxing</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrocybe ceracea</t>
+          <t>Clavulinopsis helvola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen) P.Kumm.</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73195823</v>
+        <v>67560295</v>
       </c>
       <c r="B11" t="n">
-        <v>89081</v>
+        <v>88980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4374</v>
+        <v>3295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulvaxing</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Clavulinopsis helvola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1631,13 +1655,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>347997</v>
+        <v>347998</v>
       </c>
       <c r="R11" t="n">
-        <v>6433103</v>
+        <v>6433110</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1661,12 +1685,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1687,17 +1711,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ellen Larsson, Thomas Appelqvist</t>
+          <t>Bobby Sulistyo, Patrik Lauthers, Ellen Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73195847</v>
+        <v>16591432</v>
       </c>
       <c r="B12" t="n">
-        <v>89083</v>
+        <v>88982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4377</v>
+        <v>3297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodvaxing</t>
+          <t>Aprikosfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Clavulinopsis luteoalba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Rea) Corner</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1731,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>347997</v>
+        <v>347984</v>
       </c>
       <c r="R12" t="n">
-        <v>6433103</v>
+        <v>6433120</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1761,12 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2014-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2014-09-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,17 +1811,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ellen Larsson, Thomas Appelqvist</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73195861</v>
+        <v>6948089</v>
       </c>
       <c r="B13" t="n">
-        <v>89085</v>
+        <v>89080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1805,24 +1829,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4379</v>
+        <v>4373</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Sprödvaxing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Hygrocybe ceracea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Wulfen) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1861,12 +1889,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2013-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2013-09-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,17 +1915,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ellen Larsson, Thomas Appelqvist</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>67560835</v>
+        <v>16591416</v>
       </c>
       <c r="B14" t="n">
-        <v>89055</v>
+        <v>89080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,21 +1933,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4385</v>
+        <v>4373</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Broskvaxing</t>
+          <t>Sprödvaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gliophorus laetus</t>
+          <t>Hygrocybe ceracea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Herink</t>
+          <t>(Wulfen) P.Kumm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>347997</v>
+        <v>347984</v>
       </c>
       <c r="R14" t="n">
-        <v>6433103</v>
+        <v>6433120</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1961,12 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
+          <t>2014-09-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
+          <t>2014-09-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,10 +2022,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6948086</v>
+        <v>73195823</v>
       </c>
       <c r="B15" t="n">
-        <v>89106</v>
+        <v>89081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,28 +2033,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4394</v>
+        <v>4374</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kühner</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2065,12 +2089,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2013-09-17</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2013-09-17</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,17 +2115,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Ellen Larsson, Thomas Appelqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16591411</v>
+        <v>73195847</v>
       </c>
       <c r="B16" t="n">
-        <v>89106</v>
+        <v>89083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,21 +2133,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4394</v>
+        <v>4377</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2135,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>347984</v>
+        <v>347997</v>
       </c>
       <c r="R16" t="n">
-        <v>6433120</v>
+        <v>6433103</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2165,12 +2189,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2191,17 +2215,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Ellen Larsson, Thomas Appelqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67560296</v>
+        <v>73195861</v>
       </c>
       <c r="B17" t="n">
-        <v>89106</v>
+        <v>89085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4394</v>
+        <v>4379</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,13 +2259,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>347998</v>
+        <v>347997</v>
       </c>
       <c r="R17" t="n">
-        <v>6433110</v>
+        <v>6433103</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2265,12 +2289,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2291,17 +2315,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bobby Sulistyo, Patrik Lauthers, Ellen Larsson</t>
+          <t>Ellen Larsson, Thomas Appelqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16591413</v>
+        <v>67560835</v>
       </c>
       <c r="B18" t="n">
-        <v>89035</v>
+        <v>89055</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2309,19 +2333,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4398</v>
+        <v>4385</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Broskvaxing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Gliophorus laetus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pers.) Herink</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -2331,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>347984</v>
+        <v>347997</v>
       </c>
       <c r="R18" t="n">
-        <v>6433120</v>
+        <v>6433103</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2361,12 +2389,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>67560294</v>
+        <v>6948086</v>
       </c>
       <c r="B19" t="n">
-        <v>89035</v>
+        <v>89106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,20 +2433,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4398</v>
+        <v>4394</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2427,13 +2463,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>347998</v>
+        <v>347997</v>
       </c>
       <c r="R19" t="n">
-        <v>6433110</v>
+        <v>6433103</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2457,12 +2493,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
+          <t>2013-09-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
+          <t>2013-09-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2483,17 +2519,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bobby Sulistyo, Patrik Lauthers, Ellen Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>73195881</v>
+        <v>16591411</v>
       </c>
       <c r="B20" t="n">
-        <v>89035</v>
+        <v>89106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2501,19 +2537,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4398</v>
+        <v>4394</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -2523,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>347997</v>
+        <v>347984</v>
       </c>
       <c r="R20" t="n">
-        <v>6433103</v>
+        <v>6433120</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2553,12 +2593,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2014-09-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2014-09-16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2579,59 +2619,57 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ellen Larsson, Thomas Appelqvist</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>90159538</v>
+        <v>67560296</v>
       </c>
       <c r="B21" t="n">
-        <v>102560</v>
+        <v>89106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222133</v>
+        <v>4394</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>FBF-USM, Vg</t>
+          <t>Sandhult, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>347959</v>
+        <v>347998</v>
       </c>
       <c r="R21" t="n">
-        <v>6433132</v>
+        <v>6433110</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2655,12 +2693,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2676,26 +2714,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna Stenström</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Molander, Tore Mattsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>GDP Slåtterängar och naturbetesmarker</t>
-        </is>
-      </c>
+          <t>Bobby Sulistyo, Patrik Lauthers, Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16591417</v>
+        <v>16591413</v>
       </c>
       <c r="B22" t="n">
-        <v>89087</v>
+        <v>89035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2703,11 +2737,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>239196</v>
+        <v>4398</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrocybe conica var. conica</t>
+          <t>Cuphophyllus virgineus s.lat.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -2783,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122463657</v>
+        <v>67560294</v>
       </c>
       <c r="B23" t="n">
-        <v>89079</v>
+        <v>89035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,27 +2833,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>239209</v>
+        <v>4398</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sandhult, Vg</t>
@@ -2869,16 +2903,6 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>Göteborg-Herbarium GB</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>EL305-17</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -2887,10 +2911,656 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
+          <t>Bobby Sulistyo, Patrik Lauthers, Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>73195881</v>
+      </c>
+      <c r="B24" t="n">
+        <v>89035</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4398</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sandhult, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>347997</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6433103</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Ellen Larsson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ellen Larsson, Thomas Appelqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134806006</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sandhult, Sandhult, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>348096</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6433104</v>
+      </c>
+      <c r="S25" t="n">
+        <v>7</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134806913</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sandhult, Sandhult, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>348099</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6433089</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>90159538</v>
+      </c>
+      <c r="B27" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>FBF-USM, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>347959</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6433132</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olle Molander, Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>GDP Slåtterängar och naturbetesmarker</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>16591417</v>
+      </c>
+      <c r="B28" t="n">
+        <v>89087</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>239196</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hygrocybe conica var. conica</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sandhult, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>347984</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6433120</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2014-09-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2014-09-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122463657</v>
+      </c>
+      <c r="B29" t="n">
+        <v>89079</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sandhult, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>347998</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6433110</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2017-09-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2017-09-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>Göteborg-Herbarium GB</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>EL305-17</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2093-2026 artfynd.xlsx
+++ b/artfynd/A 2093-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16591410</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560322</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122463595</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16591412</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134806595</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134806661</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134806772</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134806430</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16591428</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1715,6 +1765,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560295</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16591432</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6948089</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16591416</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73195823</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73195847</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2319,6 +2399,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73195861</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560835</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2523,6 +2613,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6948086</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16591411</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2723,6 +2823,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560296</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2819,6 +2924,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16591413</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2915,6 +3025,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560294</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3011,6 +3126,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73195881</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3132,6 +3252,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134806006</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3253,6 +3378,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134806913</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3359,6 +3489,11 @@
           <t>GDP Slåtterängar och naturbetesmarker</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90159538</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3450,6 +3585,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16591417</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3561,8 +3701,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122463657</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>